--- a/스킬정보.xlsx
+++ b/스킬정보.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="199">
   <si>
     <t>x0.875+기절 1턴</t>
   </si>
@@ -514,6 +514,8 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
       </rPr>
       <t>1.5</t>
     </r>
@@ -528,6 +530,8 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
       </rPr>
       <t>2.4</t>
     </r>
@@ -763,6 +767,146 @@
   </si>
   <si>
     <t>200~280</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>E</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>D</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>C</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>B</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>A</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>S</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>무기 등급</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>공격력</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>주무기</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>강화당 공격력</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>최대강화 레벨</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>최대주입 횟수</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>보조무기</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>무기등급</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>D</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>B</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>최대주입 횟수</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>방어구</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>방어구 등급</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>C</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>B</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>A</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>S</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>최대 방어력 합</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>각각 물방/마방 최대치</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>강화당 주스탯</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>최대주입 횟수</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>주스탯</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>액세서리</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>*무기와 방어구에는 특성이 붙어서 드랍될수있으며 특성이 붙어있으면 최대주입횟수를 +1 늘려준다</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ex)특성이 붙은 무기와 방어구는 특성을 2회 더 부여해 최대 3개의 특성을 가질수있다</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>*보조무기와 악세사리는 특성을 1개 가지고 드랍된다</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>액세서리 등급</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>최대주입 횟수</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>주스탯</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -823,13 +967,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -1105,10 +1251,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N24"/>
+  <dimension ref="A1:N52"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="16.625" customWidth="1"/>
+    <col min="1" max="1" width="20.125" customWidth="1"/>
     <col min="2" max="2" width="11" customWidth="1"/>
     <col min="7" max="7" width="9.875" customWidth="1"/>
     <col min="12" max="12" width="9" customWidth="1"/>
@@ -1123,37 +1269,37 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
-      <c r="G2" s="4"/>
-      <c r="H2" s="4"/>
-      <c r="I2" s="4"/>
-      <c r="J2" s="4"/>
-      <c r="K2" s="4"/>
-      <c r="L2" s="4"/>
-      <c r="M2" s="4"/>
-      <c r="N2" s="4"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="5"/>
+      <c r="F2" s="5"/>
+      <c r="G2" s="5"/>
+      <c r="H2" s="5"/>
+      <c r="I2" s="5"/>
+      <c r="J2" s="5"/>
+      <c r="K2" s="5"/>
+      <c r="L2" s="5"/>
+      <c r="M2" s="5"/>
+      <c r="N2" s="5"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="6" t="s">
         <v>108</v>
       </c>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4"/>
-      <c r="E3" s="4"/>
-      <c r="F3" s="4"/>
-      <c r="G3" s="4"/>
+      <c r="C3" s="5"/>
+      <c r="D3" s="5"/>
+      <c r="E3" s="5"/>
+      <c r="F3" s="5"/>
+      <c r="G3" s="5"/>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A6" s="1"/>
@@ -1336,30 +1482,30 @@
         <v>15</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A18" s="2" t="s">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A18" s="4" t="s">
         <v>149</v>
       </c>
-      <c r="B18" s="4"/>
-      <c r="C18" s="4"/>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A19" s="2" t="s">
+      <c r="B18" s="5"/>
+      <c r="C18" s="5"/>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A19" s="4" t="s">
         <v>150</v>
       </c>
-      <c r="B19" s="4"/>
-      <c r="C19" s="4"/>
-      <c r="D19" s="4"/>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A20" s="2" t="s">
+      <c r="B19" s="5"/>
+      <c r="C19" s="5"/>
+      <c r="D19" s="5"/>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A20" s="4" t="s">
         <v>159</v>
       </c>
-      <c r="B20" s="4"/>
-      <c r="C20" s="4"/>
-      <c r="D20" s="4"/>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B20" s="5"/>
+      <c r="C20" s="5"/>
+      <c r="D20" s="5"/>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
         <v>151</v>
       </c>
@@ -1382,7 +1528,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
         <v>154</v>
       </c>
@@ -1405,7 +1551,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
         <v>155</v>
       </c>
@@ -1428,7 +1574,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
         <v>158</v>
       </c>
@@ -1451,8 +1597,454 @@
         <v>163</v>
       </c>
     </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A26" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="B26" s="5"/>
+      <c r="C26" s="5"/>
+      <c r="D26" s="5"/>
+      <c r="E26" s="5"/>
+      <c r="F26" s="5"/>
+      <c r="G26" s="5"/>
+      <c r="H26" s="5"/>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A27" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="B27" s="5"/>
+      <c r="C27" s="5"/>
+      <c r="D27" s="5"/>
+      <c r="E27" s="5"/>
+      <c r="F27" s="5"/>
+      <c r="G27" s="5"/>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A28" s="1" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A29" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="G29" s="1" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A30" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="B30">
+        <v>5</v>
+      </c>
+      <c r="C30">
+        <v>15</v>
+      </c>
+      <c r="D30">
+        <v>25</v>
+      </c>
+      <c r="E30">
+        <v>45</v>
+      </c>
+      <c r="F30">
+        <v>70</v>
+      </c>
+      <c r="G30">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A31" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="B31">
+        <v>1</v>
+      </c>
+      <c r="C31">
+        <v>1</v>
+      </c>
+      <c r="D31">
+        <v>2</v>
+      </c>
+      <c r="E31">
+        <v>3</v>
+      </c>
+      <c r="F31">
+        <v>4</v>
+      </c>
+      <c r="G31">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A32" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="B32">
+        <v>5</v>
+      </c>
+      <c r="C32">
+        <v>5</v>
+      </c>
+      <c r="D32">
+        <v>5</v>
+      </c>
+      <c r="E32">
+        <v>5</v>
+      </c>
+      <c r="F32">
+        <v>5</v>
+      </c>
+      <c r="G32">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A33" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="B33">
+        <v>2</v>
+      </c>
+      <c r="C33">
+        <v>2</v>
+      </c>
+      <c r="D33">
+        <v>2</v>
+      </c>
+      <c r="E33">
+        <v>2</v>
+      </c>
+      <c r="F33">
+        <v>2</v>
+      </c>
+      <c r="G33">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A35" s="1" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A36" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="G36" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A37" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="B37">
+        <v>10</v>
+      </c>
+      <c r="C37">
+        <v>30</v>
+      </c>
+      <c r="D37">
+        <v>80</v>
+      </c>
+      <c r="E37">
+        <v>150</v>
+      </c>
+      <c r="F37">
+        <v>200</v>
+      </c>
+      <c r="G37">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A38" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="B38">
+        <v>5</v>
+      </c>
+      <c r="C38">
+        <v>15</v>
+      </c>
+      <c r="D38">
+        <v>40</v>
+      </c>
+      <c r="E38">
+        <v>75</v>
+      </c>
+      <c r="F38">
+        <v>100</v>
+      </c>
+      <c r="G38">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A39" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="B39">
+        <v>0</v>
+      </c>
+      <c r="C39">
+        <v>2</v>
+      </c>
+      <c r="D39">
+        <v>5</v>
+      </c>
+      <c r="E39">
+        <v>8</v>
+      </c>
+      <c r="F39">
+        <v>11</v>
+      </c>
+      <c r="G39">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A40" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="B40">
+        <v>1</v>
+      </c>
+      <c r="C40">
+        <v>2</v>
+      </c>
+      <c r="D40">
+        <v>3</v>
+      </c>
+      <c r="E40">
+        <v>4</v>
+      </c>
+      <c r="F40">
+        <v>5</v>
+      </c>
+      <c r="G40">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A41" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="B41">
+        <v>2</v>
+      </c>
+      <c r="C41">
+        <v>2</v>
+      </c>
+      <c r="D41">
+        <v>2</v>
+      </c>
+      <c r="E41">
+        <v>2</v>
+      </c>
+      <c r="F41">
+        <v>2</v>
+      </c>
+      <c r="G41">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A43" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="B43" s="3"/>
+      <c r="C43" s="3"/>
+      <c r="D43" s="3"/>
+      <c r="E43" s="3"/>
+      <c r="F43" s="3"/>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A44" s="1" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A45" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="E45" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="F45" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="G45" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A46" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="B46">
+        <v>0</v>
+      </c>
+      <c r="C46">
+        <v>1</v>
+      </c>
+      <c r="D46">
+        <v>3</v>
+      </c>
+      <c r="E46">
+        <v>5</v>
+      </c>
+      <c r="F46">
+        <v>7</v>
+      </c>
+      <c r="G46">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A47" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="B47">
+        <v>1</v>
+      </c>
+      <c r="C47">
+        <v>2</v>
+      </c>
+      <c r="D47">
+        <v>3</v>
+      </c>
+      <c r="E47">
+        <v>4</v>
+      </c>
+      <c r="F47">
+        <v>5</v>
+      </c>
+      <c r="G47">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A48" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="B48">
+        <v>2</v>
+      </c>
+      <c r="C48">
+        <v>2</v>
+      </c>
+      <c r="D48">
+        <v>2</v>
+      </c>
+      <c r="E48">
+        <v>2</v>
+      </c>
+      <c r="F48">
+        <v>2</v>
+      </c>
+      <c r="G48">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A50" s="1" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A51" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="E51" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="F51" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="G51" s="1" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A52" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="B52" s="7">
+        <v>3</v>
+      </c>
+      <c r="C52">
+        <v>3</v>
+      </c>
+      <c r="D52">
+        <v>3</v>
+      </c>
+      <c r="E52">
+        <v>3</v>
+      </c>
+      <c r="F52">
+        <v>3</v>
+      </c>
+      <c r="G52">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="7">
+    <mergeCell ref="A26:H26"/>
+    <mergeCell ref="A27:G27"/>
     <mergeCell ref="A18:C18"/>
     <mergeCell ref="A19:D19"/>
     <mergeCell ref="A20:D20"/>
@@ -1461,6 +2053,7 @@
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" r:id="rId1"/>
 </worksheet>
 </file>
 
